--- a/InputData/fuels/BFoICStCT/BAU Fraction of Industry Category Subject to Carbon Tax.xlsx
+++ b/InputData/fuels/BFoICStCT/BAU Fraction of Industry Category Subject to Carbon Tax.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\fuels\BFoICStCT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\fuels\BFoICStCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7220AA21-EECF-4024-B30F-3D5A7F86A6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DF0B30-6580-4E58-9EC8-118C2B0FEC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30495" yWindow="1140" windowWidth="23445" windowHeight="14565" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
+    <workbookView xWindow="8520" yWindow="2835" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -796,109 +796,112 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE28"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.26953125" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="2" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="4">
         <v>2021</v>
       </c>
-      <c r="C1" s="4">
+      <c r="D1" s="4">
         <v>2022</v>
       </c>
-      <c r="D1" s="4">
+      <c r="E1" s="4">
         <v>2023</v>
       </c>
-      <c r="E1" s="4">
+      <c r="F1" s="4">
         <v>2024</v>
       </c>
-      <c r="F1" s="4">
+      <c r="G1" s="4">
         <v>2025</v>
       </c>
-      <c r="G1" s="4">
+      <c r="H1" s="4">
         <v>2026</v>
       </c>
-      <c r="H1" s="4">
+      <c r="I1" s="4">
         <v>2027</v>
       </c>
-      <c r="I1" s="4">
+      <c r="J1" s="4">
         <v>2028</v>
       </c>
-      <c r="J1" s="4">
+      <c r="K1" s="4">
         <v>2029</v>
       </c>
-      <c r="K1" s="4">
+      <c r="L1" s="4">
         <v>2030</v>
       </c>
-      <c r="L1" s="4">
+      <c r="M1" s="4">
         <v>2031</v>
       </c>
-      <c r="M1" s="4">
+      <c r="N1" s="4">
         <v>2032</v>
       </c>
-      <c r="N1" s="4">
+      <c r="O1" s="4">
         <v>2033</v>
       </c>
-      <c r="O1" s="4">
+      <c r="P1" s="4">
         <v>2034</v>
       </c>
-      <c r="P1" s="4">
+      <c r="Q1" s="4">
         <v>2035</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="R1" s="4">
         <v>2036</v>
       </c>
-      <c r="R1" s="4">
+      <c r="S1" s="4">
         <v>2037</v>
       </c>
-      <c r="S1" s="4">
+      <c r="T1" s="4">
         <v>2038</v>
       </c>
-      <c r="T1" s="4">
+      <c r="U1" s="4">
         <v>2039</v>
       </c>
-      <c r="U1" s="4">
+      <c r="V1" s="4">
         <v>2040</v>
       </c>
-      <c r="V1" s="4">
+      <c r="W1" s="4">
         <v>2041</v>
       </c>
-      <c r="W1" s="4">
+      <c r="X1" s="4">
         <v>2042</v>
       </c>
-      <c r="X1" s="4">
+      <c r="Y1" s="4">
         <v>2043</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Z1" s="4">
         <v>2044</v>
       </c>
-      <c r="Z1" s="4">
+      <c r="AA1" s="4">
         <v>2045</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AB1" s="4">
         <v>2046</v>
       </c>
-      <c r="AB1" s="4">
+      <c r="AC1" s="4">
         <v>2047</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AD1" s="4">
         <v>2048</v>
       </c>
-      <c r="AD1" s="4">
+      <c r="AE1" s="4">
         <v>2049</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AF1" s="4">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -992,8 +995,11 @@
       <c r="AE2" s="5">
         <v>0</v>
       </c>
+      <c r="AF2" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1087,8 +1093,11 @@
       <c r="AE3" s="5">
         <v>1</v>
       </c>
+      <c r="AF3" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1182,8 +1191,11 @@
       <c r="AE4" s="5">
         <v>1</v>
       </c>
+      <c r="AF4" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1277,8 +1289,11 @@
       <c r="AE5" s="5">
         <v>1</v>
       </c>
+      <c r="AF5" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1372,8 +1387,11 @@
       <c r="AE6" s="5">
         <v>1</v>
       </c>
+      <c r="AF6" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1467,8 +1485,11 @@
       <c r="AE7" s="5">
         <v>1</v>
       </c>
+      <c r="AF7" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1562,8 +1583,11 @@
       <c r="AE8" s="5">
         <v>1</v>
       </c>
+      <c r="AF8" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1657,8 +1681,11 @@
       <c r="AE9" s="5">
         <v>1</v>
       </c>
+      <c r="AF9" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1752,8 +1779,11 @@
       <c r="AE10" s="5">
         <v>1</v>
       </c>
+      <c r="AF10" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1847,8 +1877,11 @@
       <c r="AE11" s="5">
         <v>1</v>
       </c>
+      <c r="AF11" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1942,8 +1975,11 @@
       <c r="AE12" s="5">
         <v>1</v>
       </c>
+      <c r="AF12" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2037,8 +2073,11 @@
       <c r="AE13" s="5">
         <v>1</v>
       </c>
+      <c r="AF13" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2132,8 +2171,11 @@
       <c r="AE14" s="5">
         <v>1</v>
       </c>
+      <c r="AF14" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2227,8 +2269,11 @@
       <c r="AE15" s="5">
         <v>1</v>
       </c>
+      <c r="AF15" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2322,8 +2367,11 @@
       <c r="AE16" s="5">
         <v>1</v>
       </c>
+      <c r="AF16" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2417,8 +2465,11 @@
       <c r="AE17" s="5">
         <v>1</v>
       </c>
+      <c r="AF17" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2512,8 +2563,11 @@
       <c r="AE18" s="5">
         <v>1</v>
       </c>
+      <c r="AF18" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2607,8 +2661,11 @@
       <c r="AE19" s="5">
         <v>1</v>
       </c>
+      <c r="AF19" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AE20" s="5">
         <v>1</v>
       </c>
+      <c r="AF20" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2797,8 +2857,11 @@
       <c r="AE21" s="5">
         <v>1</v>
       </c>
+      <c r="AF21" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2892,8 +2955,11 @@
       <c r="AE22" s="5">
         <v>1</v>
       </c>
+      <c r="AF22" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2987,8 +3053,11 @@
       <c r="AE23" s="5">
         <v>1</v>
       </c>
+      <c r="AF23" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3082,8 +3151,11 @@
       <c r="AE24" s="5">
         <v>1</v>
       </c>
+      <c r="AF24" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -3177,8 +3249,11 @@
       <c r="AE25" s="5">
         <v>0</v>
       </c>
+      <c r="AF25" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3272,10 +3347,14 @@
       <c r="AE26" s="5">
         <v>1</v>
       </c>
+      <c r="AF26" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3283,6 +3362,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -3426,29 +3520,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{789DCEF6-28FB-491E-AEFC-54C3E3A2768B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15B62569-EB5C-4DC0-B2C4-48F0B4FB8B41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B156FD94-677B-46CB-AFE7-2AE8298220CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B156FD94-677B-46CB-AFE7-2AE8298220CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15B62569-EB5C-4DC0-B2C4-48F0B4FB8B41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{789DCEF6-28FB-491E-AEFC-54C3E3A2768B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>